--- a/路線圖.xlsx
+++ b/路線圖.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chinqan-mac/bikedoc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421E86D1-3EF9-454F-9571-E40A731CCD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C9EA4A-8290-3F43-820E-9F11D440FB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26640" xr2:uid="{0DC60738-659B-3C4C-91C3-BEDCFE6491BC}"/>
   </bookViews>
@@ -816,15 +816,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>368301</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:colOff>711202</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>673420</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>59456</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190821</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>46756</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -839,7 +839,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="904321">
-          <a:off x="14401801" y="4356100"/>
+          <a:off x="14744702" y="3390900"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">

--- a/路線圖.xlsx
+++ b/路線圖.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chinqan-mac/bikedoc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C9EA4A-8290-3F43-820E-9F11D440FB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E663FAA-0085-6341-A989-E5476A1ABBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26640" xr2:uid="{0DC60738-659B-3C4C-91C3-BEDCFE6491BC}"/>
   </bookViews>
@@ -104,16 +104,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>12701</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>800101</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>594513</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>556413</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -136,7 +136,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3314701" y="177800"/>
+          <a:off x="800101" y="254000"/>
           <a:ext cx="17917312" cy="13271500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -155,16 +155,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>527672</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>489572</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -187,7 +187,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13208000" y="10274300"/>
+          <a:off x="10693400" y="10350500"/>
           <a:ext cx="7957172" cy="2501900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -199,16 +199,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -223,8 +223,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12382500" y="279400"/>
-          <a:ext cx="1981200" cy="1663700"/>
+          <a:off x="9410700" y="431800"/>
+          <a:ext cx="2260600" cy="1930400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -259,93 +259,93 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>起點：龍潭大池</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>貴族世家右側停車場🅿️</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:00</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>報到集合</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:20 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>作操、拍照</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:30 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>出發</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -356,16 +356,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -380,7 +380,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11366500" y="2108200"/>
+          <a:off x="8953500" y="2654300"/>
           <a:ext cx="1879600" cy="977900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -465,16 +465,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -489,7 +489,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10477500" y="6502400"/>
+          <a:off x="7962900" y="6578600"/>
           <a:ext cx="1955800" cy="1320800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -525,53 +525,53 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>1(9km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>國道三號路橋下</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>8:30~8:40</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -582,16 +582,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -606,7 +606,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11569700" y="4305300"/>
+          <a:off x="8940800" y="4394200"/>
           <a:ext cx="1879600" cy="977900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -642,7 +642,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -654,7 +654,7 @@
             <a:t>👮‍♂️內環山</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -666,7 +666,7 @@
             <a:t>(8.3km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -675,7 +675,7 @@
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -691,14 +691,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
@@ -715,8 +715,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9105900" y="10312400"/>
-          <a:ext cx="2222500" cy="1206500"/>
+          <a:off x="6388100" y="10274300"/>
+          <a:ext cx="2298700" cy="1244600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -751,60 +751,60 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給＋折返點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>(20km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7-11 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>騰達門市</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>9:30~9:40</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -815,16 +815,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>711202</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>673102</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>190821</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>152721</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>46756</xdr:rowOff>
+      <xdr:rowOff>122956</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -839,7 +839,259 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="904321">
-          <a:off x="14744702" y="3390900"/>
+          <a:off x="12230102" y="3467100"/>
+          <a:ext cx="305119" cy="465856"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>177799</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>482918</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>186456</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="向下箭號 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A725E932-C42A-0E4F-8CD8-CC6A0E9A701E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1310844">
+          <a:off x="10083799" y="7912100"/>
+          <a:ext cx="305119" cy="465856"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>305119</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>186457</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="向下箭號 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A07AA935-8061-894A-BF99-2DE034A8F116}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="863280">
+          <a:off x="9080500" y="10960101"/>
+          <a:ext cx="305119" cy="465856"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>491130</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>54967</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>796249</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>139823</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="向下箭號 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F767760A-43FA-5A4C-96E3-55822B01275B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="11945409">
+          <a:off x="10397130" y="9960967"/>
+          <a:ext cx="305119" cy="465856"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="00B050"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>334366</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>186335</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>639485</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>80691</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="向下箭號 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5244A8A2-1CE4-0144-911F-355C400DEB15}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="11920493">
+          <a:off x="11891366" y="6472835"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -879,30 +1131,30 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>215899</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>457002</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>50998</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>521018</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>110256</xdr:rowOff>
+      <xdr:colOff>762121</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>135854</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="向下箭號 27">
+        <xdr:cNvPr id="35" name="向下箭號 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A725E932-C42A-0E4F-8CD8-CC6A0E9A701E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E358A29-FE48-BF4F-B6F8-DEA662DC39E0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="1310844">
-          <a:off x="12598399" y="7835900"/>
+        <a:xfrm rot="8606604">
+          <a:off x="12839502" y="2146498"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -941,268 +1193,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>25401</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>343219</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>110257</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="向下箭號 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A07AA935-8061-894A-BF99-2DE034A8F116}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="863280">
-          <a:off x="11595100" y="10883901"/>
-          <a:ext cx="305119" cy="465856"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00B050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>529230</xdr:colOff>
+      <xdr:colOff>787400</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>169267</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>8849</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>63623</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="向下箭號 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F767760A-43FA-5A4C-96E3-55822B01275B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="11945409">
-          <a:off x="12911730" y="9884767"/>
-          <a:ext cx="305119" cy="465856"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00B050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>372466</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>110135</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>677585</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>4491</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="向下箭號 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5244A8A2-1CE4-0144-911F-355C400DEB15}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="11920493">
-          <a:off x="14405966" y="6396635"/>
-          <a:ext cx="305119" cy="465856"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00B050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>495102</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>165298</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>800221</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>59654</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="向下箭號 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E358A29-FE48-BF4F-B6F8-DEA662DC39E0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="8606604">
-          <a:off x="15354102" y="2070298"/>
-          <a:ext cx="305119" cy="465856"/>
-        </a:xfrm>
-        <a:prstGeom prst="downArrow">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00B050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent2">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent2"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent2"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1217,7 +1217,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13652500" y="8458200"/>
+          <a:off x="11137900" y="8534400"/>
           <a:ext cx="2032000" cy="1193800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1253,47 +1253,47 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>2(28.5km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>濟世宮</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
@@ -1316,16 +1316,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>749300</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1340,8 +1340,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15608300" y="4305300"/>
-          <a:ext cx="1943100" cy="1168400"/>
+          <a:off x="13106400" y="4838700"/>
+          <a:ext cx="2057400" cy="1181100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1376,47 +1376,47 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>2(35km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>中油 正新站</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
@@ -1439,16 +1439,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1463,8 +1463,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16878300" y="1397000"/>
-          <a:ext cx="2273300" cy="1244600"/>
+          <a:off x="14363700" y="1473200"/>
+          <a:ext cx="2425700" cy="1320800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1499,60 +1499,60 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>終點：龍潭大池🎈</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>11:30</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>午餐🍾</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>12:00 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>全員集合，慶生🎂</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -1563,16 +1563,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1587,7 +1587,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3403600" y="609600"/>
+          <a:off x="889000" y="685800"/>
           <a:ext cx="4889500" cy="1485900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1712,16 +1712,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1738,8 +1738,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="3441700" y="5600700"/>
-          <a:ext cx="4013200" cy="368300"/>
+          <a:off x="927100" y="5676900"/>
+          <a:ext cx="4394200" cy="444500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1764,7 +1764,7 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1780,16 +1780,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1806,8 +1806,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14363700" y="1111250"/>
-          <a:ext cx="889000" cy="234950"/>
+          <a:off x="11671300" y="1397000"/>
+          <a:ext cx="1041400" cy="63500"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1841,16 +1841,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1867,8 +1867,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="15519400" y="1219200"/>
-          <a:ext cx="1358900" cy="800100"/>
+          <a:off x="13004800" y="1295400"/>
+          <a:ext cx="1358900" cy="838200"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1902,16 +1902,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>749300</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1928,8 +1928,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="13246100" y="1854200"/>
-          <a:ext cx="1536700" cy="742950"/>
+          <a:off x="10833100" y="1905000"/>
+          <a:ext cx="1447800" cy="1238250"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1963,16 +1963,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>241300</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1989,8 +1989,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13449300" y="4794250"/>
-          <a:ext cx="546100" cy="1085850"/>
+          <a:off x="10820400" y="4883150"/>
+          <a:ext cx="635000" cy="1098550"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2024,16 +2024,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2050,7 +2050,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="12433300" y="6426200"/>
+          <a:off x="9918700" y="6502400"/>
           <a:ext cx="1397000" cy="736600"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2085,16 +2085,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>311150</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>107950</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>673100</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2111,8 +2111,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10217150" y="11518900"/>
-          <a:ext cx="361950" cy="812800"/>
+          <a:off x="7537450" y="11518900"/>
+          <a:ext cx="527050" cy="889000"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2146,16 +2146,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>444500</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2172,7 +2172,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="13017500" y="8648700"/>
+          <a:off x="10502900" y="8724900"/>
           <a:ext cx="635000" cy="406400"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -2207,16 +2207,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>711200</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>762000</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2227,12 +2227,14 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="43" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="14833600" y="4762500"/>
-          <a:ext cx="787400" cy="482600"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="12268200" y="5410200"/>
+          <a:ext cx="838200" cy="19050"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2266,16 +2268,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2290,7 +2292,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3416300" y="2336800"/>
+          <a:off x="901700" y="2413000"/>
           <a:ext cx="1562100" cy="1765300"/>
           <a:chOff x="3479800" y="6159500"/>
           <a:chExt cx="1562100" cy="1765300"/>
@@ -2419,16 +2421,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>114301</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>76201</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>73177</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>129338</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>35077</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>15038</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2443,7 +2445,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3416301" y="4445000"/>
+          <a:off x="901701" y="4521200"/>
           <a:ext cx="7388376" cy="827838"/>
           <a:chOff x="3683001" y="9029700"/>
           <a:chExt cx="7388376" cy="827838"/>

--- a/路線圖.xlsx
+++ b/路線圖.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chinqan-mac/bikedoc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E663FAA-0085-6341-A989-E5476A1ABBA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06098A4C-42A3-534B-B1AC-E976215B2948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26640" xr2:uid="{0DC60738-659B-3C4C-91C3-BEDCFE6491BC}"/>
   </bookViews>
@@ -89,6 +89,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -105,22 +110,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>800101</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>556413</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>129466</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1060" name="圖片 1059">
+        <xdr:cNvPr id="1128" name="圖片 1127">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F882AB33-75AF-F44A-E9D7-E04A1951D44B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F22E9EE2-B8D3-86A1-D557-4EF88485EDDD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -136,59 +141,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="800101" y="254000"/>
-          <a:ext cx="17917312" cy="13271500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:effectLst>
-          <a:outerShdw blurRad="470985" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-            <a:prstClr val="black">
-              <a:alpha val="72000"/>
-            </a:prstClr>
-          </a:outerShdw>
-        </a:effectLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>489572</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="圖片 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E81AA59A-3A8D-0023-048F-8298D2999198}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10693400" y="10350500"/>
-          <a:ext cx="7957172" cy="2501900"/>
+          <a:off x="723900" y="114299"/>
+          <a:ext cx="19304000" cy="13540667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -199,16 +153,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -223,8 +177,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9410700" y="431800"/>
-          <a:ext cx="2260600" cy="1930400"/>
+          <a:off x="8801100" y="190500"/>
+          <a:ext cx="2679700" cy="2070100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -259,93 +213,93 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>起點：龍潭大池</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>貴族世家右側停車場🅿️</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:00</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>報到集合</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:20 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>作操、拍照</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7:30 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>出發</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -356,16 +310,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>698500</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>406400</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -380,8 +334,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8953500" y="2654300"/>
-          <a:ext cx="1879600" cy="977900"/>
+          <a:off x="9144000" y="2717800"/>
+          <a:ext cx="1993900" cy="939800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -416,7 +370,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -428,7 +382,7 @@
             <a:t>👮‍♂️大北坑</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -440,7 +394,7 @@
             <a:t>(1km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -449,7 +403,7 @@
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1400" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -466,15 +420,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -489,8 +443,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7962900" y="6578600"/>
-          <a:ext cx="1955800" cy="1320800"/>
+          <a:off x="7518400" y="6731000"/>
+          <a:ext cx="2552700" cy="1308100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -525,53 +479,53 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>1(9km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>國道三號路橋下</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>8:30~8:40</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>8:10~8:20</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -583,15 +537,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -606,8 +560,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8940800" y="4394200"/>
-          <a:ext cx="1879600" cy="977900"/>
+          <a:off x="8801100" y="4699000"/>
+          <a:ext cx="2070100" cy="901700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -642,7 +596,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -654,7 +608,7 @@
             <a:t>👮‍♂️內環山</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -666,7 +620,7 @@
             <a:t>(8.3km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -675,7 +629,7 @@
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -692,15 +646,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>520700</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -715,8 +669,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6388100" y="10274300"/>
-          <a:ext cx="2298700" cy="1244600"/>
+          <a:off x="6146800" y="10566400"/>
+          <a:ext cx="2628900" cy="1371600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -751,60 +705,60 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給＋折返點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>(20km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>7-11 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>騰達門市</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>9:30~9:40</a:t>
-          </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>9:20~9:30</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -815,16 +769,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>673102</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>304802</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>12701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>152721</xdr:colOff>
+      <xdr:colOff>609921</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>122956</xdr:rowOff>
+      <xdr:rowOff>97557</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -839,7 +793,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="904321">
-          <a:off x="12230102" y="3467100"/>
+          <a:off x="12687302" y="3441701"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -879,15 +833,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>177799</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>393699</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>482918</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>186456</xdr:rowOff>
+      <xdr:colOff>698818</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>34056</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -901,8 +855,8 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="1310844">
-          <a:off x="10083799" y="7912100"/>
+        <a:xfrm rot="902880">
+          <a:off x="10299699" y="8140700"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -942,15 +896,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>101601</xdr:rowOff>
+      <xdr:colOff>177799</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>127001</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>305119</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>186457</xdr:rowOff>
+      <xdr:colOff>482918</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>21357</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -965,7 +919,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="863280">
-          <a:off x="9080500" y="10960101"/>
+          <a:off x="9258299" y="11176001"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -1005,15 +959,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>491130</xdr:colOff>
+      <xdr:colOff>795931</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>54967</xdr:rowOff>
+      <xdr:rowOff>67668</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>796249</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>275550</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>139823</xdr:rowOff>
+      <xdr:rowOff>152524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1027,8 +981,8 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="11945409">
-          <a:off x="10397130" y="9960967"/>
+        <a:xfrm rot="11918839">
+          <a:off x="10701931" y="9973668"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -1068,15 +1022,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>334366</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>186335</xdr:rowOff>
+      <xdr:colOff>626465</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>160934</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>639485</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>80691</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>106084</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>55290</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1091,7 +1045,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="11920493">
-          <a:off x="11891366" y="6472835"/>
+          <a:off x="12183465" y="6637934"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -1130,16 +1084,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>457002</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>50998</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76003</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>12898</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>762121</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>135854</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>381122</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>97754</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1153,8 +1107,8 @@
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
-        <a:xfrm rot="8606604">
-          <a:off x="12839502" y="2146498"/>
+        <a:xfrm rot="9130509">
+          <a:off x="13284003" y="2489398"/>
           <a:ext cx="305119" cy="465856"/>
         </a:xfrm>
         <a:prstGeom prst="downArrow">
@@ -1193,16 +1147,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>787400</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1217,8 +1171,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11137900" y="8534400"/>
-          <a:ext cx="2032000" cy="1193800"/>
+          <a:off x="11747500" y="8420100"/>
+          <a:ext cx="2425700" cy="1397000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1253,51 +1207,58 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>2(28.5km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>濟世宮</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="2000" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>濟</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>世宮</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>10:00~10:40</a:t>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>10:00~10:10</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
@@ -1316,16 +1277,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1340,8 +1301,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13106400" y="4838700"/>
-          <a:ext cx="2057400" cy="1181100"/>
+          <a:off x="13309600" y="5054600"/>
+          <a:ext cx="2565400" cy="1320800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1376,51 +1337,51 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>🍖補給點</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>2(35km)</a:t>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>3(35km)</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>中油 正新站</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+          <a:endParaRPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>時間：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
-              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
-            </a:rPr>
-            <a:t>11:00~11:10</a:t>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>10:40~10:50</a:t>
           </a:r>
           <a:br>
             <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0">
@@ -1440,15 +1401,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1463,8 +1424,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14363700" y="1473200"/>
-          <a:ext cx="2425700" cy="1320800"/>
+          <a:off x="14719300" y="1041400"/>
+          <a:ext cx="2755900" cy="1384300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1499,60 +1460,60 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>終點：龍潭大池🎈</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>11:30</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>午餐🍾</a:t>
           </a:r>
           <a:br>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>12:00 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" baseline="0">
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
             <a:t>全員集合，慶生🎂</a:t>
           </a:r>
-          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0">
+          <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0">
             <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
           </a:endParaRPr>
@@ -1570,9 +1531,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1588,7 +1549,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="889000" y="685800"/>
-          <a:ext cx="4889500" cy="1485900"/>
+          <a:ext cx="4914900" cy="1803400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1664,7 +1625,7 @@
             </a:rPr>
           </a:br>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
@@ -1674,36 +1635,118 @@
             <a:t>報名日期：</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
-            <a:t>5/9~5/14</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" baseline="0">
+            <a:t>5/9(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
-            <a:t>活動時間：</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="zh-TW" sz="1600" b="1" i="0" baseline="0">
+            <a:t>六</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
-            <a:t>5/24</a:t>
+            <a:t>)~5/14(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>四</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>活動時間：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>5/24(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>日</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>總里程：</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-TW" sz="1800" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+              <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
+            </a:rPr>
+            <a:t>41KM</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1713,15 +1756,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>368300</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1738,8 +1781,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="927100" y="5676900"/>
-          <a:ext cx="4394200" cy="444500"/>
+          <a:off x="901700" y="6477000"/>
+          <a:ext cx="4622800" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1764,14 +1807,14 @@
             <a:defRPr sz="1000"/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="zh-TW" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="zh-TW" altLang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
             </a:rPr>
-            <a:t>自帶：水水水，車燈，內胎，簡易工具，雨具</a:t>
+            <a:t>自帶：水，車燈，內胎，簡易工具，雨具</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1780,16 +1823,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
+      <xdr:colOff>711200</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1806,8 +1849,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11671300" y="1397000"/>
-          <a:ext cx="1041400" cy="63500"/>
+          <a:off x="11480800" y="1225550"/>
+          <a:ext cx="1612900" cy="260350"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1841,16 +1884,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1867,8 +1910,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="13004800" y="1295400"/>
-          <a:ext cx="1358900" cy="838200"/>
+          <a:off x="13208000" y="1358900"/>
+          <a:ext cx="1511300" cy="374650"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1903,15 +1946,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>101600</xdr:colOff>
+      <xdr:colOff>406400</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1928,8 +1971,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="10833100" y="1905000"/>
-          <a:ext cx="1447800" cy="1238250"/>
+          <a:off x="11137900" y="1955800"/>
+          <a:ext cx="1447800" cy="1231900"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1964,15 +2007,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1989,8 +2032,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10820400" y="4883150"/>
-          <a:ext cx="635000" cy="1098550"/>
+          <a:off x="10871200" y="5149850"/>
+          <a:ext cx="812800" cy="1085850"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2025,15 +2068,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2050,8 +2093,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="9918700" y="6502400"/>
-          <a:ext cx="1397000" cy="736600"/>
+          <a:off x="10071100" y="6870700"/>
+          <a:ext cx="1536700" cy="514350"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2086,15 +2129,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>107950</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2111,8 +2154,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7537450" y="11518900"/>
-          <a:ext cx="527050" cy="889000"/>
+          <a:off x="7461250" y="11938000"/>
+          <a:ext cx="692150" cy="1003300"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2147,15 +2190,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>596900</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>749300</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>406400</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2172,8 +2215,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="10502900" y="8724900"/>
-          <a:ext cx="635000" cy="406400"/>
+          <a:off x="10655300" y="9080500"/>
+          <a:ext cx="1092200" cy="38100"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2207,16 +2250,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>711200</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2233,8 +2276,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="12268200" y="5410200"/>
-          <a:ext cx="838200" cy="19050"/>
+          <a:off x="12471400" y="5626100"/>
+          <a:ext cx="838200" cy="88900"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -2269,15 +2312,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2292,7 +2335,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="901700" y="2413000"/>
+          <a:off x="889000" y="2959100"/>
           <a:ext cx="1562100" cy="1765300"/>
           <a:chOff x="3479800" y="6159500"/>
           <a:chExt cx="1562100" cy="1765300"/>
@@ -2356,7 +2399,7 @@
                 <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
                 <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               </a:rPr>
-              <a:t>飛騎ＱＲ </a:t>
+              <a:t>飛騎</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
@@ -2366,7 +2409,7 @@
                 <a:latin typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
                 <a:ea typeface="Microsoft JhengHei" panose="020B0604030504040204" pitchFamily="34" charset="-120"/>
               </a:rPr>
-              <a:t>code</a:t>
+              <a:t> QR code</a:t>
             </a:r>
             <a:br>
               <a:rPr lang="en-US" altLang="zh-TW" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0">
@@ -2401,7 +2444,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2422,15 +2465,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>76201</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>35077</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>15038</xdr:rowOff>
+      <xdr:colOff>60476</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>40438</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -2445,7 +2488,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="901701" y="4521200"/>
+          <a:off x="927100" y="8166100"/>
           <a:ext cx="7388376" cy="827838"/>
           <a:chOff x="3683001" y="9029700"/>
           <a:chExt cx="7388376" cy="827838"/>
@@ -2465,7 +2508,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2494,7 +2537,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -2509,6 +2552,192 @@
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>585633</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>108572</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="1104" name="群組 1103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE5F909F-477D-BDB4-55A2-9C199F4A34EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="11317133" y="10845800"/>
+          <a:ext cx="8603439" cy="2705100"/>
+          <a:chOff x="10047133" y="10756900"/>
+          <a:chExt cx="8603439" cy="2705100"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="1102" name="群組 1101">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDA5D399-20A5-4A64-90C8-E0C99DBA620F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="10047133" y="10756900"/>
+            <a:ext cx="8603439" cy="2705100"/>
+            <a:chOff x="10047133" y="10756900"/>
+            <a:chExt cx="8603439" cy="2705100"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="4" name="圖片 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E81AA59A-3A8D-0023-048F-8298D2999198}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10047133" y="10756900"/>
+              <a:ext cx="8603439" cy="2705100"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1101" name="矩形 1100">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD63785-D506-58B1-2CB8-F3517D86AF94}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10706100" y="11328400"/>
+              <a:ext cx="2146300" cy="431800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="1103" name="矩形 1102">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DB1AAE2-D79B-F842-AB79-6F84D7905D28}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="10097933" y="11341100"/>
+            <a:ext cx="1370167" cy="355600"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>

--- a/路線圖.xlsx
+++ b/路線圖.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06098A4C-42A3-534B-B1AC-E976215B2948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26640" xr2:uid="{0DC60738-659B-3C4C-91C3-BEDCFE6491BC}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19440" xr2:uid="{0DC60738-659B-3C4C-91C3-BEDCFE6491BC}"/>
   </bookViews>
   <sheets>
     <sheet name="路線圖" sheetId="1" r:id="rId1"/>
